--- a/docs/review/packs/chapter-3.5.xlsx
+++ b/docs/review/packs/chapter-3.5.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Treat the lateral compartment as the more meniscus dependent one, on the ground that it has no bony concavity.</t>
+          <t>Read a contact area figure with its load, flexion angle and method attached, since all three change it.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Expect extrusion or a root tear to reduce contact area without removing tissue.</t>
+          <t>Treat the lateral compartment as the more meniscus dependent one, on the ground that it has no bony concavity.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Expect deep flexion to be a small area position, and therefore a high stress one.</t>
+          <t>Expect extrusion or a root tear to reduce contact area without removing tissue.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Treat contact area as the quantity a reconstruction restores and a measurement cannot confirm.</t>
+          <t>Expect deep flexion to be a small area position, and therefore a high stress one.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Repair rather than resect where the ring can be restored, on area grounds.</t>
+          <t>Treat contact area as the quantity a reconstruction restores and a measurement cannot confirm.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>- Tissue present is not necessarily tissue working; the ring must be anchored.</t>
+          <t>Repair rather than resect where the ring can be restored, on area grounds.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -2091,22 +2091,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.5.2-P1</t>
+          <t>3.5.1-P7</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3.5.2</t>
+          <t>3.5.1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Treat a halved contact area as a doubled stress, which is the arithmetic behind the meniscectomy literature.</t>
+          <t>Correct alignment alongside any area restoring procedure, since malalignment concentrates load regardless.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2116,22 +2116,22 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.5.2-P2</t>
+          <t>3.5.1-P8</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3.5.2</t>
+          <t>3.5.1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Consider shear as well as compression when a delamination or osteochondral lesion is the problem.</t>
+          <t>State that contact area cannot be measured clinically when explaining why a procedure's mechanical case rests on cadaveric work.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2141,12 +2141,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.5.2-P3</t>
+          <t>3.5.1-P9</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3.5.2</t>
+          <t>3.5.1</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Treat peak contact stress as the common currency of every mechanical argument in the knee.</t>
+          <t>- Tissue present is not necessarily tissue working; the ring must be anchored.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.5.2-P4</t>
+          <t>3.5.2-P1</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Expect a cartilage repair of different stiffness to distribute load differently from the original.</t>
+          <t>Treat a halved contact area as a doubled stress, which is the arithmetic behind the meniscectomy literature.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2191,12 +2191,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P1</t>
+          <t>3.5.2-P2</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.5.3</t>
+          <t>3.5.2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Assess lateral soft tissue integrity when a medial overload picture is worse than the alignment explains.</t>
+          <t>Consider shear as well as compression when a delamination or osteochondral lesion is the problem.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2216,12 +2216,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P2</t>
+          <t>3.5.2-P3</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.5.3</t>
+          <t>3.5.2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Treat the adduction moment as the measurable proxy for the division.</t>
+          <t>Read an in vivo stress figure as a model output rather than a measurement.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2241,22 +2241,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P3</t>
+          <t>3.5.2-P4</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3.5.3</t>
+          <t>3.5.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Expect the division to vary through a step rather than holding at a quoted average.</t>
+          <t>Treat peak contact stress as the common currency of every mechanical argument in the knee.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2266,12 +2266,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P4</t>
+          <t>3.5.2-P5</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3.5.3</t>
+          <t>3.5.2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Treat the division as the target of unicompartmental and realignment surgery, and treat the published average as a starting point rather than a patient's number.</t>
+          <t>Expect a cartilage repair of different stiffness to distribute load differently from the original.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2291,12 +2291,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P5</t>
+          <t>3.5.2-P6</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>3.5.3</t>
+          <t>3.5.2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Assess the opposite compartment and the cruciate before unicompartmental replacement, since the operation relies on them.</t>
+          <t>State that no in vivo stress threshold is established when a patient asks how much load is safe.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P6</t>
+          <t>3.5.3-P1</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Plan correction to avoid transferring an excessive share, rather than to the largest achievable angle.</t>
+          <t>Assess lateral soft tissue integrity when a medial overload picture is worse than the alignment explains.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P7</t>
+          <t>3.5.3-P2</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Use long leg alignment as the clinical proxy for the division.</t>
+          <t>Treat the adduction moment as the measurable proxy for the division.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P8</t>
+          <t>3.5.3-P3</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Expect the division to change as the unoperated compartment progresses.</t>
+          <t>Expect the division to vary through a step rather than holding at a quoted average.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2391,22 +2391,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P1</t>
+          <t>3.5.3-P4</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.5.4</t>
+          <t>3.5.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Expect posterior horn symptoms in deep flexion and absence of findings in mid range testing.</t>
+          <t>Treat the division as the target of unicompartmental and realignment surgery, and treat the published average as a starting point rather than a patient's number.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2416,22 +2416,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P2</t>
+          <t>3.5.3-P5</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.5.4</t>
+          <t>3.5.3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Treat the thinness of the deep flexion literature as a limit on confidence rather than as reassurance.</t>
+          <t>Assess the opposite compartment and the cruciate before unicompartmental replacement, since the operation relies on them.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P3</t>
+          <t>3.5.3-P6</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.5.4</t>
+          <t>3.5.3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Treat deep flexion as a design constraint with a stated cost.</t>
+          <t>Plan correction to avoid transferring an excessive share, rather than to the largest achievable angle.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2466,12 +2466,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P4</t>
+          <t>3.5.3-P7</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.5.4</t>
+          <t>3.5.3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Restore posterior condylar offset rather than accepting an approximation.</t>
+          <t>Use long leg alignment as the clinical proxy for the division.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2491,12 +2491,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P5</t>
+          <t>3.5.3-P8</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.5.4</t>
+          <t>3.5.3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Expect the deep flexion contact area to be small, and choose the bearing accordingly.</t>
+          <t>Expect the division to change as the unoperated compartment progresses.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P6</t>
+          <t>3.5.4-P1</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Repair posterior horn roots where feasible, on deep flexion loading grounds.</t>
+          <t>Expect posterior horn symptoms in deep flexion and absence of findings in mid range testing.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2541,12 +2541,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P1</t>
+          <t>3.5.4-P2</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.5.5</t>
+          <t>3.5.4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Resect as little as the tear requires, since the stress rise scales with the resection.</t>
+          <t>Treat the thinness of the deep flexion literature as a limit on confidence rather than as reassurance.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2566,22 +2566,22 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P2</t>
+          <t>3.5.4-P3</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.5.5</t>
+          <t>3.5.4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Preserve the peripheral rim and the roots, which carry the hoop tension.</t>
+          <t>Treat deep flexion as a design constraint with a stated cost.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2591,22 +2591,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P3</t>
+          <t>3.5.4-P4</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.5.5</t>
+          <t>3.5.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Repair a root tear on the same grounds as a meniscal tear, because mechanically it is one.</t>
+          <t>Restore posterior condylar offset rather than accepting an approximation.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2616,12 +2616,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P4</t>
+          <t>3.5.4-P5</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.5.5</t>
+          <t>3.5.4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Treat the contact studies as the mechanical case for preservation and the cohorts as the clinical one, and note that they agree.</t>
+          <t>Expect the deep flexion contact area to be small, and choose the bearing accordingly.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P5</t>
+          <t>3.5.4-P6</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.5.5</t>
+          <t>3.5.4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Repair of a root restores the hoop mechanism if it restores the attachment at the right position and tension, which is the mechanical reason anatomic repair is specified rather than preferred.</t>
+          <t>Repair posterior horn roots where feasible, on deep flexion loading grounds.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2666,7 +2666,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P6</t>
+          <t>3.5.5-P1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Repair rather than resect wherever the hoop mechanism can be restored.</t>
+          <t>Resect as little as the tear requires, since the stress rise scales with the resection.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2691,12 +2691,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P1</t>
+          <t>3.5.5-P2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.5.6</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment standing and on a long leg film, since supine imaging underestimates it.</t>
+          <t>Preserve the peripheral rim and the roots, which carry the hoop tension.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2716,12 +2716,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P2</t>
+          <t>3.5.5-P3</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.5.6</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Localise the deformity to the femur, the tibia or the joint before planning a correction.</t>
+          <t>Repair a root tear on the same grounds as a meniscal tear, because mechanically it is one.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2741,12 +2741,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P3</t>
+          <t>3.5.5-P4</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.5.6</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Treat the adduction moment as the quantity alignment is a proxy for.</t>
+          <t>Read extrusion as a functional loss even where the meniscus is continuous.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P4</t>
+          <t>3.5.5-P5</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.5.6</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Treat alignment as the only mechanical variable in this chapter that can be changed by a large amount.</t>
+          <t>Treat the contact studies as the mechanical case for preservation and the cohorts as the clinical one, and note that they agree.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2791,12 +2791,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P5</t>
+          <t>3.5.5-P6</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.5.6</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Assess slope separately, since it acts on a different mechanism from compartment share.</t>
+          <t>Repair of a root restores the hoop mechanism if it restores the attachment at the right position and tension, which is the mechanical reason anatomic repair is specified rather than preferred.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2816,22 +2816,22 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P1</t>
+          <t>3.5.5-P7</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.5.7</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Expect gait adaptation to offset part of the scaling, so the effect is real and smaller than pure arithmetic.</t>
+          <t>Repair rather than resect wherever the hoop mechanism can be restored.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2841,22 +2841,22 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P2</t>
+          <t>3.5.5-P8</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.5.7</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Address alignment alongside weight, since it decides where the amplified load falls.</t>
+          <t>Correct alignment alongside preservation or transplantation, or the restored area is overloaded.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2866,22 +2866,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P3</t>
+          <t>3.5.6-P1</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.5.7</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Treat mass as a mechanical variable with the largest achievable effect size and the lowest achievement rate, which is an uncomfortable combination rather than a reason to leave it out.</t>
+          <t>Measure alignment standing and on a long leg film, since supine imaging underestimates it.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2891,22 +2891,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P4</t>
+          <t>3.5.6-P2</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.5.7</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Discuss mass as a mechanical factor in construct survival, with the registry evidence named.</t>
+          <t>Localise the deformity to the femur, the tibia or the joint before planning a correction.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2916,22 +2916,22 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P5</t>
+          <t>3.5.6-P3</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.5.7</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Use the association for counselling rather than as an exclusion, since it does not predict an individual.</t>
+          <t>Treat the adduction moment as the quantity alignment is a proxy for.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2941,22 +2941,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P1</t>
+          <t>3.5.6-P4</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.5.8</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Treat a chronically deficient knee as mechanically different from an acutely injured one, not simply as a later stage.</t>
+          <t>Treat alignment as the only mechanical variable in this chapter that can be changed by a large amount.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2966,22 +2966,22 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P2</t>
+          <t>3.5.6-P5</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.5.8</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where translation is larger than the injury explains.</t>
+          <t>Correct alignment before or with any cartilage or meniscal procedure in a malaligned limb.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2991,12 +2991,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P3</t>
+          <t>3.5.6-P6</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.5.8</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Treat the contact shift as the mechanical account of post-traumatic degeneration after cruciate injury, and treat it as only partly addressable.</t>
+          <t>Assess slope separately, since it acts on a different mechanism from compartment share.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3016,12 +3016,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P4</t>
+          <t>3.5.6-P7</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.5.8</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>It restores stability reliably and contact position partially, so counselling about long term joint health should not rest on the first achievement alone.</t>
+          <t>Confirm the correction radiographically rather than assuming the plan was achieved.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3041,22 +3041,22 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P5</t>
+          <t>3.5.7-P1</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.5.8</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Repair a ramp lesion alongside reconstruction, on secondary restraint grounds.</t>
+          <t>Expect gait adaptation to offset part of the scaling, so the effect is real and smaller than pure arithmetic.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3066,22 +3066,22 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P6</t>
+          <t>3.5.7-P2</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.5.8</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in revision and in a graft that failed without a new injury.</t>
+          <t>Address alignment alongside weight, since it decides where the amplified load falls.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3091,22 +3091,22 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P1</t>
+          <t>3.5.7-P3</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.5.9</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Repair where the tear allows it preserves the ring and therefore the pressure.</t>
+          <t>State that mechanical and metabolic effects both operate and cannot be separated in an individual.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3116,22 +3116,22 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P2</t>
+          <t>3.5.7-P4</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.5.9</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Resect the minimum the tear requires, and record what was resected.</t>
+          <t>Treat mass as a mechanical variable with the largest achievable effect size and the lowest achievement rate, which is an uncomfortable combination rather than a reason to leave it out.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3141,22 +3141,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P3</t>
+          <t>3.5.7-P5</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.5.9</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Treat a young lateral meniscectomy as the worst mechanical combination and counsel accordingly.</t>
+          <t>Discuss mass as a mechanical factor in construct survival, with the registry evidence named.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3166,12 +3166,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P4</t>
+          <t>3.5.7-P6</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.5.9</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Treat the dose response as the mechanical justification for the shift from resection to repair, and note that the shift was mechanically predicted before it was clinically demonstrated.</t>
+          <t>Correct alignment in a heavier patient, since the amplified load needs directing.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3191,12 +3191,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P5</t>
+          <t>3.5.7-P7</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.5.9</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Repair rather than resect wherever the ring can be restored, in a young patient above all.</t>
+          <t>Use the association for counselling rather than as an exclusion, since it does not predict an individual.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P1</t>
+          <t>3.5.8-P1</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Plan to a mechanical axis target rather than a correction angle alone.</t>
+          <t>Treat a chronically deficient knee as mechanically different from an acutely injured one, not simply as a later stage.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3241,12 +3241,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P2</t>
+          <t>3.5.8-P2</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Assess the receiving compartment before correcting load into it.</t>
+          <t>Measure slope where translation is larger than the injury explains.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P3</t>
+          <t>3.5.8-P3</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.8</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Treat osteotomy as the mechanical foundation that other procedures are built on, rather than as an alternative to them.</t>
+          <t>Treat the contact shift as the mechanical account of post-traumatic degeneration after cruciate injury, and treat it as only partly addressable.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3291,12 +3291,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P4</t>
+          <t>3.5.8-P4</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.8</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Localise the deformity before correcting, and confirm the achieved axis afterwards.</t>
+          <t>It restores stability reliably and contact position partially, so counselling about long term joint health should not rest on the first achievement alone.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3316,12 +3316,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P5</t>
+          <t>3.5.8-P5</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3331,16 +3331,391 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Treat slope correction as a separate operation with its own indication.</t>
+          <t>Repair a ramp lesion alongside reconstruction, on secondary restraint grounds.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3.5.8-P6</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>3.5.8</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Measure slope in revision and in a graft that failed without a new injury.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9-P1</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Repair where the tear allows it preserves the ring and therefore the pressure.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9-P2</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Resect the minimum the tear requires, and record what was resected.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9-P3</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Treat a young lateral meniscectomy as the worst mechanical combination and counsel accordingly.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9-P4</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Treat the dose response as the mechanical justification for the shift from resection to repair, and note that the shift was mechanically predicted before it was clinically demonstrated.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9-P5</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Repair rather than resect wherever the ring can be restored, in a young patient above all.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9-P6</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Offer transplantation for symptoms with an honest account of its cartilage protection evidence.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9-P7</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>3.5.9</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment in a meniscus deficient compartment before expecting any restoration to hold.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P1</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Plan to a mechanical axis target rather than a correction angle alone.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P2</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Assess the receiving compartment before correcting load into it.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P3</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the achieved axis radiographically, since the plan and the result can differ.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P4</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Treat osteotomy as the mechanical foundation that other procedures are built on, rather than as an alternative to them.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P5</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment as the foundation for cartilage and meniscal work rather than as an alternative.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P6</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Localise the deformity before correcting, and confirm the achieved axis afterwards.</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P7</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Treat slope correction as a separate operation with its own indication.</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3731,7 +4106,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>56</f>
+        <f>71</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -3746,7 +4121,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -3776,7 +4151,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -3788,7 +4163,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -3800,7 +4175,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -3812,7 +4187,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.5.xlsx
+++ b/docs/review/packs/chapter-3.5.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Treat a halved contact area as a doubled stress, which is the arithmetic behind the meniscectomy literature.</t>
+          <t>Ask for peak rather than average contact stress when reading a comparative study.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Consider shear as well as compression when a delamination or osteochondral lesion is the problem.</t>
+          <t>Treat a halved contact area as a doubled stress, which is the arithmetic behind the meniscectomy literature.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Read an in vivo stress figure as a model output rather than a measurement.</t>
+          <t>Consider shear as well as compression when a delamination or osteochondral lesion is the problem.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Treat peak contact stress as the common currency of every mechanical argument in the knee.</t>
+          <t>Read an in vivo stress figure as a model output rather than a measurement.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Expect a cartilage repair of different stiffness to distribute load differently from the original.</t>
+          <t>Treat peak contact stress as the common currency of every mechanical argument in the knee.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>State that no in vivo stress threshold is established when a patient asks how much load is safe.</t>
+          <t>Expect a cartilage repair of different stiffness to distribute load differently from the original.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2316,22 +2316,22 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P1</t>
+          <t>3.5.2-P7</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3.5.3</t>
+          <t>3.5.2</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Assess lateral soft tissue integrity when a medial overload picture is worse than the alignment explains.</t>
+          <t>State that no in vivo stress threshold is established when a patient asks how much load is safe.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P2</t>
+          <t>3.5.3-P1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Treat the adduction moment as the measurable proxy for the division.</t>
+          <t>Assess lateral soft tissue integrity when a medial overload picture is worse than the alignment explains.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P3</t>
+          <t>3.5.3-P2</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Expect the division to vary through a step rather than holding at a quoted average.</t>
+          <t>Treat the adduction moment as the measurable proxy for the division.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P4</t>
+          <t>3.5.3-P3</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Treat the division as the target of unicompartmental and realignment surgery, and treat the published average as a starting point rather than a patient's number.</t>
+          <t>Expect the division to vary through a step rather than holding at a quoted average.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P5</t>
+          <t>3.5.3-P4</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Assess the opposite compartment and the cruciate before unicompartmental replacement, since the operation relies on them.</t>
+          <t>Treat the division as the target of unicompartmental and realignment surgery, and treat the published average as a starting point rather than a patient's number.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P6</t>
+          <t>3.5.3-P5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Plan correction to avoid transferring an excessive share, rather than to the largest achievable angle.</t>
+          <t>Assess the opposite compartment and the cruciate before unicompartmental replacement, since the operation relies on them.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2466,7 +2466,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P7</t>
+          <t>3.5.3-P6</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Use long leg alignment as the clinical proxy for the division.</t>
+          <t>Plan correction to avoid transferring an excessive share, rather than to the largest achievable angle.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.5.3-P8</t>
+          <t>3.5.3-P7</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Expect the division to change as the unoperated compartment progresses.</t>
+          <t>Use long leg alignment as the clinical proxy for the division.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2516,22 +2516,22 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P1</t>
+          <t>3.5.3-P8</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.5.4</t>
+          <t>3.5.3</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Expect posterior horn symptoms in deep flexion and absence of findings in mid range testing.</t>
+          <t>Expect the division to change as the unoperated compartment progresses.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2541,7 +2541,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P2</t>
+          <t>3.5.4-P1</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Treat the thinness of the deep flexion literature as a limit on confidence rather than as reassurance.</t>
+          <t>Record the flexion angle with any contact measurement, since all three quantities move with it.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P3</t>
+          <t>3.5.4-P2</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Treat deep flexion as a design constraint with a stated cost.</t>
+          <t>Expect posterior horn symptoms in deep flexion and absence of findings in mid range testing.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P4</t>
+          <t>3.5.4-P3</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Restore posterior condylar offset rather than accepting an approximation.</t>
+          <t>Treat the thinness of the deep flexion literature as a limit on confidence rather than as reassurance.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2616,7 +2616,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P5</t>
+          <t>3.5.4-P4</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Expect the deep flexion contact area to be small, and choose the bearing accordingly.</t>
+          <t>Treat deep flexion as a design constraint with a stated cost.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2641,7 +2641,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.5.4-P6</t>
+          <t>3.5.4-P5</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Repair posterior horn roots where feasible, on deep flexion loading grounds.</t>
+          <t>Restore posterior condylar offset rather than accepting an approximation.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2666,22 +2666,22 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P1</t>
+          <t>3.5.4-P6</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.5.5</t>
+          <t>3.5.4</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Resect as little as the tear requires, since the stress rise scales with the resection.</t>
+          <t>Expect the deep flexion contact area to be small, and choose the bearing accordingly.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2691,22 +2691,22 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P2</t>
+          <t>3.5.4-P7</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.5.5</t>
+          <t>3.5.4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Preserve the peripheral rim and the roots, which carry the hoop tension.</t>
+          <t>Repair posterior horn roots where feasible, on deep flexion loading grounds.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P3</t>
+          <t>3.5.5-P1</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Repair a root tear on the same grounds as a meniscal tear, because mechanically it is one.</t>
+          <t>Resect as little as the tear requires, since the stress rise scales with the resection.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P4</t>
+          <t>3.5.5-P2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Read extrusion as a functional loss even where the meniscus is continuous.</t>
+          <t>Preserve the peripheral rim and the roots, which carry the hoop tension.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2766,7 +2766,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P5</t>
+          <t>3.5.5-P3</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Treat the contact studies as the mechanical case for preservation and the cohorts as the clinical one, and note that they agree.</t>
+          <t>Repair a root tear on the same grounds as a meniscal tear, because mechanically it is one.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P6</t>
+          <t>3.5.5-P4</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Repair of a root restores the hoop mechanism if it restores the attachment at the right position and tension, which is the mechanical reason anatomic repair is specified rather than preferred.</t>
+          <t>Read extrusion as a functional loss even where the meniscus is continuous.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P7</t>
+          <t>3.5.5-P5</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Repair rather than resect wherever the hoop mechanism can be restored.</t>
+          <t>Treat the contact studies as the mechanical case for preservation and the cohorts as the clinical one, and note that they agree.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.5.5-P8</t>
+          <t>3.5.5-P6</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment alongside preservation or transplantation, or the restored area is overloaded.</t>
+          <t>Repair of a root restores the hoop mechanism if it restores the attachment at the right position and tension, which is the mechanical reason anatomic repair is specified rather than preferred.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2866,22 +2866,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P1</t>
+          <t>3.5.5-P7</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.5.6</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment standing and on a long leg film, since supine imaging underestimates it.</t>
+          <t>Repair rather than resect wherever the hoop mechanism can be restored.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2891,22 +2891,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P2</t>
+          <t>3.5.5-P8</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.5.6</t>
+          <t>3.5.5</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Localise the deformity to the femur, the tibia or the joint before planning a correction.</t>
+          <t>Correct alignment alongside preservation or transplantation, or the restored area is overloaded.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P3</t>
+          <t>3.5.6-P1</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Treat the adduction moment as the quantity alignment is a proxy for.</t>
+          <t>Measure alignment standing and on a long leg film, since supine imaging underestimates it.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2941,7 +2941,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P4</t>
+          <t>3.5.6-P2</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Treat alignment as the only mechanical variable in this chapter that can be changed by a large amount.</t>
+          <t>Localise the deformity to the femur, the tibia or the joint before planning a correction.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2966,7 +2966,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P5</t>
+          <t>3.5.6-P3</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment before or with any cartilage or meniscal procedure in a malaligned limb.</t>
+          <t>Treat the adduction moment as the quantity alignment is a proxy for.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P6</t>
+          <t>3.5.6-P4</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Assess slope separately, since it acts on a different mechanism from compartment share.</t>
+          <t>Treat alignment as the only mechanical variable in this chapter that can be changed by a large amount.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3016,7 +3016,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.5.6-P7</t>
+          <t>3.5.6-P5</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Confirm the correction radiographically rather than assuming the plan was achieved.</t>
+          <t>Correct alignment before or with any cartilage or meniscal procedure in a malaligned limb.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3041,22 +3041,22 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P1</t>
+          <t>3.5.6-P6</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.5.7</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Expect gait adaptation to offset part of the scaling, so the effect is real and smaller than pure arithmetic.</t>
+          <t>Assess slope separately, since it acts on a different mechanism from compartment share.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3066,22 +3066,22 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P2</t>
+          <t>3.5.6-P7</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.5.7</t>
+          <t>3.5.6</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Address alignment alongside weight, since it decides where the amplified load falls.</t>
+          <t>Confirm the correction radiographically rather than assuming the plan was achieved.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3091,7 +3091,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P3</t>
+          <t>3.5.7-P1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>State that mechanical and metabolic effects both operate and cannot be separated in an individual.</t>
+          <t>Expect gait adaptation to offset part of the scaling, so the effect is real and smaller than pure arithmetic.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P4</t>
+          <t>3.5.7-P2</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Treat mass as a mechanical variable with the largest achievable effect size and the lowest achievement rate, which is an uncomfortable combination rather than a reason to leave it out.</t>
+          <t>Address alignment alongside weight, since it decides where the amplified load falls.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3141,7 +3141,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P5</t>
+          <t>3.5.7-P3</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Discuss mass as a mechanical factor in construct survival, with the registry evidence named.</t>
+          <t>State that mechanical and metabolic effects both operate and cannot be separated in an individual.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3166,7 +3166,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P6</t>
+          <t>3.5.7-P4</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment in a heavier patient, since the amplified load needs directing.</t>
+          <t>Treat mass as a mechanical variable with the largest achievable effect size and the lowest achievement rate, which is an uncomfortable combination rather than a reason to leave it out.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3191,7 +3191,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.5.7-P7</t>
+          <t>3.5.7-P5</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Use the association for counselling rather than as an exclusion, since it does not predict an individual.</t>
+          <t>Discuss mass as a mechanical factor in construct survival, with the registry evidence named.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3216,22 +3216,22 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P1</t>
+          <t>3.5.7-P6</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.5.8</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Treat a chronically deficient knee as mechanically different from an acutely injured one, not simply as a later stage.</t>
+          <t>Correct alignment in a heavier patient, since the amplified load needs directing.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3241,22 +3241,22 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P2</t>
+          <t>3.5.7-P7</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.5.8</t>
+          <t>3.5.7</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where translation is larger than the injury explains.</t>
+          <t>Use the association for counselling rather than as an exclusion, since it does not predict an individual.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3266,7 +3266,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P3</t>
+          <t>3.5.8-P1</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Treat the contact shift as the mechanical account of post-traumatic degeneration after cruciate injury, and treat it as only partly addressable.</t>
+          <t>Treat a chronically deficient knee as mechanically different from an acutely injured one, not simply as a later stage.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P4</t>
+          <t>3.5.8-P2</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>It restores stability reliably and contact position partially, so counselling about long term joint health should not rest on the first achievement alone.</t>
+          <t>Measure slope where translation is larger than the injury explains.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P5</t>
+          <t>3.5.8-P3</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Repair a ramp lesion alongside reconstruction, on secondary restraint grounds.</t>
+          <t>Treat the contact shift as the mechanical account of post-traumatic degeneration after cruciate injury, and treat it as only partly addressable.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3341,7 +3341,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.5.8-P6</t>
+          <t>3.5.8-P4</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in revision and in a graft that failed without a new injury.</t>
+          <t>It restores stability reliably and contact position partially, so counselling about long term joint health should not rest on the first achievement alone.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3366,22 +3366,22 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P1</t>
+          <t>3.5.8-P5</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>3.5.9</t>
+          <t>3.5.8</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Repair where the tear allows it preserves the ring and therefore the pressure.</t>
+          <t>Repair a ramp lesion alongside reconstruction, on secondary restraint grounds.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3391,22 +3391,22 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P2</t>
+          <t>3.5.8-P6</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>3.5.9</t>
+          <t>3.5.8</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Resect the minimum the tear requires, and record what was resected.</t>
+          <t>Measure slope in revision and in a graft that failed without a new injury.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3416,22 +3416,22 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P3</t>
+          <t>3.5.8-P7</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>3.5.9</t>
+          <t>3.5.8</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Treat a young lateral meniscectomy as the worst mechanical combination and counsel accordingly.</t>
+          <t>Counsel that stability and long term joint health are different outcomes.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P4</t>
+          <t>3.5.9-P1</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Treat the dose response as the mechanical justification for the shift from resection to repair, and note that the shift was mechanically predicted before it was clinically demonstrated.</t>
+          <t>Repair where the tear allows it preserves the ring and therefore the pressure.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3466,7 +3466,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P5</t>
+          <t>3.5.9-P2</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Repair rather than resect wherever the ring can be restored, in a young patient above all.</t>
+          <t>Resect the minimum the tear requires, and record what was resected.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P6</t>
+          <t>3.5.9-P3</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Offer transplantation for symptoms with an honest account of its cartilage protection evidence.</t>
+          <t>Treat a young lateral meniscectomy as the worst mechanical combination and counsel accordingly.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3516,7 +3516,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.5.9-P7</t>
+          <t>3.5.9-P4</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment in a meniscus deficient compartment before expecting any restoration to hold.</t>
+          <t>Treat the dose response as the mechanical justification for the shift from resection to repair, and note that the shift was mechanically predicted before it was clinically demonstrated.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3541,22 +3541,22 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P1</t>
+          <t>3.5.9-P5</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.9</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Plan to a mechanical axis target rather than a correction angle alone.</t>
+          <t>Repair rather than resect wherever the ring can be restored, in a young patient above all.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -3566,22 +3566,22 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P2</t>
+          <t>3.5.9-P6</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.9</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Assess the receiving compartment before correcting load into it.</t>
+          <t>Offer transplantation for symptoms with an honest account of its cartilage protection evidence.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3591,22 +3591,22 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P3</t>
+          <t>3.5.9-P7</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.9</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Confirm the achieved axis radiographically, since the plan and the result can differ.</t>
+          <t>Correct alignment in a meniscus deficient compartment before expecting any restoration to hold.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -3616,12 +3616,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P4</t>
+          <t>3.5.9-P8</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>3.5.10</t>
+          <t>3.5.9</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Treat osteotomy as the mechanical foundation that other procedures are built on, rather than as an alternative to them.</t>
+          <t>Record the resection precisely, since the next surgeon's options depend on it.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3641,7 +3641,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P5</t>
+          <t>3.5.10-P1</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment as the foundation for cartilage and meniscal work rather than as an alternative.</t>
+          <t>Plan to a mechanical axis target rather than a correction angle alone.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
@@ -3666,7 +3666,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P6</t>
+          <t>3.5.10-P2</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Localise the deformity before correcting, and confirm the achieved axis afterwards.</t>
+          <t>Assess the receiving compartment before correcting load into it.</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -3691,7 +3691,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>3.5.10-P7</t>
+          <t>3.5.10-P3</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -3701,21 +3701,146 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Treat slope correction as a separate operation with its own indication.</t>
+          <t>Confirm the achieved axis radiographically, since the plan and the result can differ.</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P4</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Treat osteotomy as the mechanical foundation that other procedures are built on, rather than as an alternative to them.</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P5</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment as the foundation for cartilage and meniscal work rather than as an alternative.</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P6</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Localise the deformity before correcting, and confirm the achieved axis afterwards.</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P7</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Counsel that the correction changes any later arthroplasty.</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10-P8</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>3.5.10</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Treat slope correction as a separate operation with its own indication.</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4106,7 +4231,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>71</f>
+        <f>76</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -4121,7 +4246,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E73,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E78,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -4151,7 +4276,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E73,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E78,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -4163,7 +4288,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E73,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E78,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -4175,7 +4300,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E73,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E78,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -4187,7 +4312,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E73,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E78,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
